--- a/public/templates/teacher-import-template.xlsx
+++ b/public/templates/teacher-import-template.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F575AF95-3B31-4CEB-9410-FA19E0B5EEA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BE7B3B-EFDC-4828-82AE-34D607949349}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Teachers" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="179021"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>Employee ID</t>
   </si>
@@ -28,9 +28,6 @@
     <t>First Name</t>
   </si>
   <si>
-    <t>Middle Name</t>
-  </si>
-  <si>
     <t>Last Name</t>
   </si>
   <si>
@@ -40,9 +37,6 @@
     <t>Phone</t>
   </si>
   <si>
-    <t>Subjects</t>
-  </si>
-  <si>
     <t>Grade-Sections (Teaching)</t>
   </si>
   <si>
@@ -55,21 +49,9 @@
     <t>10 - Amorsolo</t>
   </si>
   <si>
-    <t>Jao</t>
-  </si>
-  <si>
-    <t>Austin</t>
-  </si>
-  <si>
     <t>Dela Cruz</t>
   </si>
   <si>
-    <t>jaodelacruz@example.com</t>
-  </si>
-  <si>
-    <t>FIL</t>
-  </si>
-  <si>
     <t>REQUIRED</t>
   </si>
   <si>
@@ -77,6 +59,12 @@
   </si>
   <si>
     <t>OPTIONal</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>juandelacruz@example.com</t>
   </si>
 </sst>
 </file>
@@ -476,21 +464,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" customWidth="1"/>
-    <col min="8" max="8" width="33.140625" customWidth="1"/>
-    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,80 +492,62 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1067</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" xr:uid="{54EAA2A0-D56B-4A7E-9AE4-CC8CB888BA8D}"/>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{54EAA2A0-D56B-4A7E-9AE4-CC8CB888BA8D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
